--- a/2026/Proyecto_Final/drive_proyecto_final/Técnico/Iluminación + Matafuegos.xlsx
+++ b/2026/Proyecto_Final/drive_proyecto_final/Técnico/Iluminación + Matafuegos.xlsx
@@ -16,16 +16,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="124">
   <si>
+    <t>Sector de incendio</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Sector / puesto</t>
+  </si>
+  <si>
     <t>Volumenes de produccion</t>
-  </si>
-  <si>
-    <t>Sector de incendio</t>
-  </si>
-  <si>
-    <t>Sector / puesto</t>
-  </si>
-  <si>
-    <t>N</t>
   </si>
   <si>
     <t>Superficie
@@ -40,14 +40,25 @@
  200 m2</t>
   </si>
   <si>
+    <t>Largo
+ (m)</t>
+  </si>
+  <si>
     <t>Por distancia
  maxima</t>
   </si>
   <si>
+    <t>Ancho
+ (m)</t>
+  </si>
+  <si>
     <t>Adoptados</t>
   </si>
   <si>
     <t>Capacidad</t>
+  </si>
+  <si>
+    <t>Alto (m)</t>
   </si>
   <si>
     <t>SI-1 Deposito MP + Aduana</t>
@@ -74,94 +85,26 @@
  (MJ)</t>
   </si>
   <si>
-    <t>Largo
- (m)</t>
-  </si>
-  <si>
-    <t>Ancho
- (m)</t>
-  </si>
-  <si>
-    <t>A</t>
+    <t>IL</t>
+  </si>
+  <si>
+    <t>kg/año</t>
   </si>
   <si>
     <t>SI-1 Deposito MP + Aduana [1]+[2]</t>
   </si>
   <si>
-    <t>kg/año</t>
+    <t>Cantida de mediciones</t>
   </si>
   <si>
     <t>Consumo anual de MP - linea panificados</t>
-  </si>
-  <si>
-    <t>Consumo anual de MP total</t>
-  </si>
-  <si>
-    <t>10 L</t>
-  </si>
-  <si>
-    <t>Alto (m)</t>
-  </si>
-  <si>
-    <t>SI-2 Nave de produccion - general</t>
-  </si>
-  <si>
-    <t>Dias activos por ano</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>A / B</t>
-  </si>
-  <si>
-    <t>Consumo diario de MP</t>
-  </si>
-  <si>
-    <t>kg/d</t>
-  </si>
-  <si>
-    <t>10 kg</t>
-  </si>
-  <si>
-    <t>Rendimiento global MP a PT</t>
-  </si>
-  <si>
-    <t>IL</t>
-  </si>
-  <si>
-    <t>SI-2 Tablero horno tunel [6]</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Produccion anual de PT</t>
-  </si>
-  <si>
-    <t>5 kg</t>
-  </si>
-  <si>
-    <t>Produccion diaria de PT</t>
-  </si>
-  <si>
-    <t>SI-2 Tablero hornos rotativos [12]</t>
-  </si>
-  <si>
-    <t>Cantida de mediciones</t>
-  </si>
-  <si>
-    <t>SI-2 Envasadoras [8] y [14]</t>
-  </si>
-  <si>
-    <t>Politica de stock</t>
   </si>
   <si>
     <t>Sup.
  (m2)</t>
+  </si>
+  <si>
+    <t>Consumo anual de MP total</t>
   </si>
   <si>
     <t>Minimo
@@ -169,98 +112,176 @@
  (lx)</t>
   </si>
   <si>
-    <t>Dias de stock de materia prima</t>
-  </si>
-  <si>
     <t>Nivel de
  diseno
  (lx)</t>
   </si>
   <si>
+    <t>Dias activos por ano</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>Consumo diario de MP</t>
+  </si>
+  <si>
+    <t>kg/d</t>
+  </si>
+  <si>
+    <t>Harinas, feculas, almidones y azucares</t>
+  </si>
+  <si>
+    <t>Rendimiento global MP a PT</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Deposito MP</t>
+  </si>
+  <si>
+    <t>Produccion anual de PT</t>
+  </si>
+  <si>
+    <t>Produccion diaria de PT</t>
+  </si>
+  <si>
+    <t>Politica de stock</t>
+  </si>
+  <si>
+    <t>Dias de stock de materia prima</t>
+  </si>
+  <si>
+    <t>Grasas y aceites vegetales</t>
+  </si>
+  <si>
+    <t>Dias de stock de producto terminado</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>Stock de MP almacenado</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Pallets de madera</t>
+  </si>
+  <si>
+    <t>Stock de PT almacenado</t>
+  </si>
+  <si>
+    <t>Bobinas de film en deposito</t>
+  </si>
+  <si>
+    <t>10 L</t>
+  </si>
+  <si>
+    <t>Poderes calorificos inferiores</t>
+  </si>
+  <si>
+    <t>Madera - patron de referencia</t>
+  </si>
+  <si>
+    <t>Carton plano en deposito</t>
+  </si>
+  <si>
+    <t>MJ/kg</t>
+  </si>
+  <si>
+    <t>SI-2 Nave de produccion - general</t>
+  </si>
+  <si>
+    <t>A / B</t>
+  </si>
+  <si>
+    <t>Energia total del sector</t>
+  </si>
+  <si>
+    <t>10 kg</t>
+  </si>
+  <si>
+    <t>SI-2 Tablero horno tunel [6]</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Carton corrugado</t>
+  </si>
+  <si>
+    <t>5 kg</t>
+  </si>
+  <si>
+    <t>SI-2 Tablero hornos rotativos [12]</t>
+  </si>
+  <si>
+    <t>Film de polipropileno</t>
+  </si>
+  <si>
+    <t>SI-2 Envasadoras [8] y [14]</t>
+  </si>
+  <si>
+    <t>SI-2 Nave de produccion [3] a [14],[16],[17],[18]</t>
+  </si>
+  <si>
     <t>SI-2 Laboratorio Calidad Cocido [18]</t>
   </si>
   <si>
+    <t>Composicion y existencias auxiliares</t>
+  </si>
+  <si>
     <t>B / C</t>
   </si>
   <si>
-    <t>Dias de stock de producto terminado</t>
-  </si>
-  <si>
-    <t>Stock de MP almacenado</t>
+    <t>Producto en proceso</t>
   </si>
   <si>
     <t>SI-3 Deposito de PT</t>
   </si>
   <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Stock de PT almacenado</t>
-  </si>
-  <si>
-    <t>Deposito MP</t>
+    <t>Fraccion de grasas sobre el total de MP</t>
+  </si>
+  <si>
+    <t>Bobinas de film montadas</t>
+  </si>
+  <si>
+    <t>Pallets en deposito de MP</t>
   </si>
   <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>Poderes calorificos inferiores</t>
-  </si>
-  <si>
-    <t>Madera - patron de referencia</t>
-  </si>
-  <si>
-    <t>MJ/kg</t>
-  </si>
-  <si>
-    <t>Harinas, feculas, almidones y azucares</t>
-  </si>
-  <si>
-    <t>Grasas y aceites vegetales</t>
-  </si>
-  <si>
-    <t>Carton corrugado</t>
-  </si>
-  <si>
-    <t>Film de polipropileno</t>
-  </si>
-  <si>
-    <t>Composicion y existencias auxiliares</t>
-  </si>
-  <si>
-    <t>Fraccion de grasas sobre el total de MP</t>
-  </si>
-  <si>
-    <t>Pallets en deposito de MP</t>
-  </si>
-  <si>
     <t>u</t>
   </si>
   <si>
     <t>Pallets en deposito de PT</t>
   </si>
   <si>
+    <t>Cajas armadas</t>
+  </si>
+  <si>
     <t>Peso unitario del pallet</t>
   </si>
   <si>
     <t>Stock de film en deposito</t>
   </si>
   <si>
+    <t>Pallets en transito</t>
+  </si>
+  <si>
     <t>Stock de carton en deposito</t>
   </si>
   <si>
-    <t>Pallets de madera</t>
-  </si>
-  <si>
     <t>Producto en proceso en la nave</t>
   </si>
   <si>
     <t>Bobinas de film montadas en linea</t>
   </si>
   <si>
-    <t>Bobinas de film en deposito</t>
-  </si>
-  <si>
     <t>Cajas armadas en encajonado</t>
   </si>
   <si>
@@ -270,55 +291,19 @@
     <t>Carton de las cajas del PT almacenado</t>
   </si>
   <si>
-    <t>Carton plano en deposito</t>
+    <t>SI-3 Deposito de PT [15]</t>
   </si>
   <si>
     <t>Film del PT almacenado</t>
   </si>
   <si>
-    <t>Energia total del sector</t>
-  </si>
-  <si>
-    <t>SI-2 Nave de produccion [3] a [14],[16],[17],[18]</t>
-  </si>
-  <si>
-    <t>Producto en proceso</t>
-  </si>
-  <si>
-    <t>Bobinas de film montadas</t>
-  </si>
-  <si>
-    <t>Cajas armadas</t>
-  </si>
-  <si>
-    <t>Pallets en transito</t>
-  </si>
-  <si>
-    <t>Aduana MP (recepcion y control)</t>
-  </si>
-  <si>
-    <t>SI-3 Deposito de PT [15]</t>
-  </si>
-  <si>
-    <t>Seccion Pesado (macro y micro)</t>
-  </si>
-  <si>
     <t>Producto terminado envasado</t>
   </si>
   <si>
     <t>Carton de cajas</t>
   </si>
   <si>
-    <t>Amasado</t>
-  </si>
-  <si>
     <t>Film de envases</t>
-  </si>
-  <si>
-    <t>Moldeado</t>
-  </si>
-  <si>
-    <t>Horno Tunel</t>
   </si>
   <si>
     <t>Sector</t>
@@ -334,9 +319,6 @@
     <t>Riesgo</t>
   </si>
   <si>
-    <t>Cinta Enfriado</t>
-  </si>
-  <si>
     <t>Potencial
  clase A</t>
   </si>
@@ -345,37 +327,55 @@
  clase B</t>
   </si>
   <si>
+    <t>Mas de 100 kg/m2</t>
+  </si>
+  <si>
+    <t>Riesgo 3 - Muy combustible</t>
+  </si>
+  <si>
+    <t>6A</t>
+  </si>
+  <si>
+    <t>Aduana MP (recepcion y control)</t>
+  </si>
+  <si>
+    <t>10B</t>
+  </si>
+  <si>
+    <t>SI-2 Nave de produccion</t>
+  </si>
+  <si>
+    <t>Hasta 15 kg/m2</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>Seccion Pesado (macro y micro)</t>
+  </si>
+  <si>
+    <t>NAVE COMPLETA sin muros cortafuego</t>
+  </si>
+  <si>
+    <t>Amasado</t>
+  </si>
+  <si>
+    <t>Moldeado</t>
+  </si>
+  <si>
+    <t>Horno Tunel</t>
+  </si>
+  <si>
+    <t>Cinta Enfriado</t>
+  </si>
+  <si>
     <t>Envasado 1</t>
   </si>
   <si>
-    <t>Mas de 100 kg/m2</t>
-  </si>
-  <si>
     <t>Batido Panif.</t>
-  </si>
-  <si>
-    <t>Riesgo 3 - Muy combustible</t>
-  </si>
-  <si>
-    <t>6A</t>
-  </si>
-  <si>
-    <t>10B</t>
-  </si>
-  <si>
-    <t>SI-2 Nave de produccion</t>
-  </si>
-  <si>
-    <t>Hasta 15 kg/m2</t>
-  </si>
-  <si>
-    <t>1A</t>
-  </si>
-  <si>
-    <t>4B</t>
-  </si>
-  <si>
-    <t>NAVE COMPLETA sin muros cortafuego</t>
   </si>
   <si>
     <t>Dosificado</t>
@@ -421,12 +421,17 @@
     </font>
     <font>
       <b/>
-      <color theme="1"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -435,18 +440,13 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -472,12 +472,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EEF7"/>
-        <bgColor rgb="FFE8EEF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF1F3864"/>
         <bgColor rgb="FF1F3864"/>
       </patternFill>
@@ -486,6 +480,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8EEF7"/>
+        <bgColor rgb="FFE8EEF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -534,90 +534,90 @@
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="2" fillId="3" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="8" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="2" xfId="0" applyFont="1" applyNumberFormat="1"/>
@@ -860,35 +860,35 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="11" t="s">
+      <c r="C1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="G1" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>48</v>
+      <c r="I1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="2">
@@ -896,7 +896,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C2" s="15">
         <v>8.3</v>
@@ -907,7 +907,7 @@
       <c r="E2" s="15">
         <v>6.5</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="22">
         <f t="shared" ref="F2:F19" si="1">D2*C2/(E2*(C2+D2))</f>
         <v>0.5510010537</v>
       </c>
@@ -915,7 +915,7 @@
         <f t="shared" ref="G2:G19" si="2">(F2+2)^2</f>
         <v>6.507606376</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="26">
         <f t="shared" ref="H2:H19" si="3">C2*D2</f>
         <v>52.29</v>
       </c>
@@ -931,7 +931,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="C3" s="15">
         <v>3.8</v>
@@ -942,7 +942,7 @@
       <c r="E3" s="15">
         <v>6.5</v>
       </c>
-      <c r="F3" s="20">
+      <c r="F3" s="22">
         <f t="shared" si="1"/>
         <v>0.2923076923</v>
       </c>
@@ -950,7 +950,7 @@
         <f t="shared" si="2"/>
         <v>5.254674556</v>
       </c>
-      <c r="H3" s="24">
+      <c r="H3" s="26">
         <f t="shared" si="3"/>
         <v>14.44</v>
       </c>
@@ -966,7 +966,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C4" s="15">
         <v>2.0</v>
@@ -977,7 +977,7 @@
       <c r="E4" s="15">
         <v>6.5</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="22">
         <f t="shared" si="1"/>
         <v>0.2015915119</v>
       </c>
@@ -985,7 +985,7 @@
         <f t="shared" si="2"/>
         <v>4.847005185</v>
       </c>
-      <c r="H4" s="24">
+      <c r="H4" s="26">
         <f t="shared" si="3"/>
         <v>7.6</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C5" s="15">
         <v>2.4</v>
@@ -1012,7 +1012,7 @@
       <c r="E5" s="15">
         <v>6.5</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="22">
         <f t="shared" si="1"/>
         <v>0.1765886288</v>
       </c>
@@ -1020,7 +1020,7 @@
         <f t="shared" si="2"/>
         <v>4.737538059</v>
       </c>
-      <c r="H5" s="24">
+      <c r="H5" s="26">
         <f t="shared" si="3"/>
         <v>5.28</v>
       </c>
@@ -1036,7 +1036,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C6" s="15">
         <v>2.5</v>
@@ -1047,7 +1047,7 @@
       <c r="E6" s="15">
         <v>6.5</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="22">
         <f t="shared" si="1"/>
         <v>0.1842948718</v>
       </c>
@@ -1055,7 +1055,7 @@
         <f t="shared" si="2"/>
         <v>4.771144087</v>
       </c>
-      <c r="H6" s="24">
+      <c r="H6" s="26">
         <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
@@ -1071,7 +1071,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="C7" s="15">
         <v>8.6</v>
@@ -1082,7 +1082,7 @@
       <c r="E7" s="15">
         <v>6.5</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="22">
         <f t="shared" si="1"/>
         <v>0.2791813691</v>
       </c>
@@ -1090,7 +1090,7 @@
         <f t="shared" si="2"/>
         <v>5.194667713</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="26">
         <f t="shared" si="3"/>
         <v>19.78</v>
       </c>
@@ -1106,7 +1106,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="C8" s="15">
         <v>7.0</v>
@@ -1117,7 +1117,7 @@
       <c r="E8" s="15">
         <v>6.5</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="22">
         <f t="shared" si="1"/>
         <v>0.1575984991</v>
       </c>
@@ -1125,7 +1125,7 @@
         <f t="shared" si="2"/>
         <v>4.655231283</v>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="26">
         <f t="shared" si="3"/>
         <v>8.4</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="C9" s="15">
         <v>4.3</v>
@@ -1152,7 +1152,7 @@
       <c r="E9" s="15">
         <v>6.5</v>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="22">
         <f t="shared" si="1"/>
         <v>0.3188137164</v>
       </c>
@@ -1160,7 +1160,7 @@
         <f t="shared" si="2"/>
         <v>5.376897051</v>
       </c>
-      <c r="H9" s="24">
+      <c r="H9" s="26">
         <f t="shared" si="3"/>
         <v>17.2</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C10" s="15">
         <v>2.2</v>
@@ -1187,7 +1187,7 @@
       <c r="E10" s="15">
         <v>6.5</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="22">
         <f t="shared" si="1"/>
         <v>0.1425101215</v>
       </c>
@@ -1195,7 +1195,7 @@
         <f t="shared" si="2"/>
         <v>4.590349621</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="26">
         <f t="shared" si="3"/>
         <v>3.52</v>
       </c>
@@ -1222,7 +1222,7 @@
       <c r="E11" s="15">
         <v>6.5</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="22">
         <f t="shared" si="1"/>
         <v>0.1318681319</v>
       </c>
@@ -1230,7 +1230,7 @@
         <f t="shared" si="2"/>
         <v>4.544861732</v>
       </c>
-      <c r="H11" s="24">
+      <c r="H11" s="26">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
@@ -1257,7 +1257,7 @@
       <c r="E12" s="15">
         <v>6.5</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="22">
         <f t="shared" si="1"/>
         <v>0.1025641026</v>
       </c>
@@ -1265,7 +1265,7 @@
         <f t="shared" si="2"/>
         <v>4.420775805</v>
       </c>
-      <c r="H12" s="24">
+      <c r="H12" s="26">
         <f t="shared" si="3"/>
         <v>1.8</v>
       </c>
@@ -1292,7 +1292,7 @@
       <c r="E13" s="15">
         <v>6.5</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="22">
         <f t="shared" si="1"/>
         <v>0.3325842697</v>
       </c>
@@ -1300,7 +1300,7 @@
         <f t="shared" si="2"/>
         <v>5.440949375</v>
       </c>
-      <c r="H13" s="24">
+      <c r="H13" s="26">
         <f t="shared" si="3"/>
         <v>19.24</v>
       </c>
@@ -1327,7 +1327,7 @@
       <c r="E14" s="15">
         <v>6.5</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="22">
         <f t="shared" si="1"/>
         <v>0.1739130435</v>
       </c>
@@ -1335,7 +1335,7 @@
         <f t="shared" si="2"/>
         <v>4.725897921</v>
       </c>
-      <c r="H14" s="24">
+      <c r="H14" s="26">
         <f t="shared" si="3"/>
         <v>5.2</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="E15" s="15">
         <v>6.5</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="22">
         <f t="shared" si="1"/>
         <v>0.3692307692</v>
       </c>
@@ -1370,7 +1370,7 @@
         <f t="shared" si="2"/>
         <v>5.613254438</v>
       </c>
-      <c r="H15" s="24">
+      <c r="H15" s="26">
         <f t="shared" si="3"/>
         <v>23.04</v>
       </c>
@@ -1397,7 +1397,7 @@
       <c r="E16" s="15">
         <v>6.5</v>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="22">
         <f t="shared" si="1"/>
         <v>1.043478261</v>
       </c>
@@ -1405,7 +1405,7 @@
         <f t="shared" si="2"/>
         <v>9.262759924</v>
       </c>
-      <c r="H16" s="24">
+      <c r="H16" s="26">
         <f t="shared" si="3"/>
         <v>187.2</v>
       </c>
@@ -1432,7 +1432,7 @@
       <c r="E17" s="15">
         <v>6.5</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="22">
         <f t="shared" si="1"/>
         <v>0.1821036107</v>
       </c>
@@ -1440,7 +1440,7 @@
         <f t="shared" si="2"/>
         <v>4.761576168</v>
       </c>
-      <c r="H17" s="24">
+      <c r="H17" s="26">
         <f t="shared" si="3"/>
         <v>5.8</v>
       </c>
@@ -1467,7 +1467,7 @@
       <c r="E18" s="15">
         <v>6.5</v>
       </c>
-      <c r="F18" s="20">
+      <c r="F18" s="22">
         <f t="shared" si="1"/>
         <v>0.1346153846</v>
       </c>
@@ -1475,7 +1475,7 @@
         <f t="shared" si="2"/>
         <v>4.55658284</v>
       </c>
-      <c r="H18" s="24">
+      <c r="H18" s="26">
         <f t="shared" si="3"/>
         <v>3.15</v>
       </c>
@@ -1502,7 +1502,7 @@
       <c r="E19" s="15">
         <v>6.5</v>
       </c>
-      <c r="F19" s="20">
+      <c r="F19" s="22">
         <f t="shared" si="1"/>
         <v>0.2655426765</v>
       </c>
@@ -1510,7 +1510,7 @@
         <f t="shared" si="2"/>
         <v>5.132683619</v>
       </c>
-      <c r="H19" s="24">
+      <c r="H19" s="26">
         <f t="shared" si="3"/>
         <v>12.6</v>
       </c>
@@ -5458,373 +5458,373 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3"/>
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="4"/>
       <c r="C1" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>15</v>
+      <c r="A2" s="7" t="s">
+        <v>18</v>
       </c>
       <c r="B2" s="9">
         <v>431449.0</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>22</v>
+      <c r="A3" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="B3" s="9">
         <v>395371.0</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" s="8">
+      <c r="A4" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="13">
         <v>826820.0</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>27</v>
+      <c r="A5" s="7" t="s">
+        <v>29</v>
       </c>
       <c r="B5" s="9">
         <v>239.0</v>
       </c>
-      <c r="C5" s="10" t="s">
-        <v>28</v>
+      <c r="C5" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="8">
+      <c r="A6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="13">
         <v>3459.497908</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>31</v>
+      <c r="C6" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>33</v>
+      <c r="A7" s="7" t="s">
+        <v>34</v>
       </c>
       <c r="B7" s="9">
         <v>0.9</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>36</v>
+      <c r="C7" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="13">
+        <v>744138.0</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="8">
-        <v>744138.0</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="B9" s="13">
+        <v>3113.548117</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="B9" s="8">
-        <v>3113.548117</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="B12" s="9">
         <v>15.0</v>
       </c>
-      <c r="C12" s="10" t="s">
-        <v>28</v>
+      <c r="C12" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
-        <v>51</v>
+      <c r="A13" s="7" t="s">
+        <v>42</v>
       </c>
       <c r="B13" s="9">
         <v>15.0</v>
       </c>
-      <c r="C13" s="10" t="s">
-        <v>28</v>
+      <c r="C13" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="8">
+      <c r="A14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" s="13">
         <v>51892.46862</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>54</v>
+      <c r="C14" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B15" s="8">
+      <c r="A15" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="13">
         <v>46703.22176</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>54</v>
+      <c r="C15" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B17" s="3"/>
+      <c r="A17" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B17" s="4"/>
       <c r="C17" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
-        <v>59</v>
+      <c r="A18" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="B18" s="9">
         <v>18.41</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>60</v>
+      <c r="C18" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="s">
-        <v>61</v>
+      <c r="A19" s="7" t="s">
+        <v>33</v>
       </c>
       <c r="B19" s="9">
         <v>16.5</v>
       </c>
-      <c r="C19" s="10" t="s">
-        <v>60</v>
+      <c r="C19" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>62</v>
+      <c r="A20" s="7" t="s">
+        <v>41</v>
       </c>
       <c r="B20" s="9">
         <v>38.0</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="B21" s="9">
         <v>17.0</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>60</v>
+      <c r="C21" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="s">
-        <v>64</v>
+      <c r="A22" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="B22" s="9">
         <v>44.0</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>60</v>
+      <c r="C22" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="3"/>
+      <c r="A24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="4"/>
       <c r="C24" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="s">
-        <v>66</v>
+      <c r="A25" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="B25" s="9">
         <v>0.08</v>
       </c>
-      <c r="C25" s="10" t="s">
-        <v>36</v>
+      <c r="C25" s="11" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="s">
-        <v>67</v>
+      <c r="A26" s="7" t="s">
+        <v>73</v>
       </c>
       <c r="B26" s="9">
         <v>74.0</v>
       </c>
-      <c r="C26" s="10" t="s">
-        <v>68</v>
+      <c r="C26" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="s">
-        <v>69</v>
+      <c r="A27" s="7" t="s">
+        <v>76</v>
       </c>
       <c r="B27" s="9">
         <v>80.0</v>
       </c>
-      <c r="C27" s="10" t="s">
-        <v>68</v>
+      <c r="C27" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="s">
-        <v>70</v>
+      <c r="A28" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="B28" s="9">
         <v>25.0</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>54</v>
+      <c r="C28" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="s">
-        <v>71</v>
+      <c r="A29" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="B29" s="9">
         <v>1293.0</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>54</v>
+      <c r="C29" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="s">
-        <v>72</v>
+      <c r="A30" s="7" t="s">
+        <v>81</v>
       </c>
       <c r="B30" s="9">
         <v>3916.0</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>54</v>
+      <c r="C30" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="8">
+      <c r="A31" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B31" s="13">
         <v>1153.165969</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>54</v>
+      <c r="C31" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="s">
-        <v>75</v>
+      <c r="A32" s="7" t="s">
+        <v>83</v>
       </c>
       <c r="B32" s="9">
         <v>300.0</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>54</v>
+      <c r="C32" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="s">
-        <v>77</v>
+      <c r="A33" s="7" t="s">
+        <v>84</v>
       </c>
       <c r="B33" s="9">
         <v>500.0</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>54</v>
+      <c r="C33" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="s">
-        <v>78</v>
+      <c r="A34" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="B34" s="9">
         <v>15.0</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>68</v>
+      <c r="C34" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B35" s="8">
+      <c r="A35" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="13">
         <v>3736.257741</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>54</v>
+      <c r="C35" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B36" s="8">
+      <c r="A36" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B36" s="13">
         <v>373.6257741</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>54</v>
+      <c r="C36" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -5840,474 +5840,474 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="17">
+        <v>47741.0</v>
+      </c>
+      <c r="D3" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="E3" s="17">
+        <v>787728.0</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="14"/>
+      <c r="B4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="17">
+        <v>4151.0</v>
+      </c>
+      <c r="D4" s="11">
+        <v>38.0</v>
+      </c>
+      <c r="E4" s="17">
+        <v>157753.0</v>
+      </c>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="14"/>
+      <c r="B5" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="17">
+        <v>1850.0</v>
+      </c>
+      <c r="D5" s="11">
+        <v>18.4</v>
+      </c>
+      <c r="E5" s="17">
+        <v>34059.0</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14"/>
+      <c r="B6" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="17">
+        <v>1293.0</v>
+      </c>
+      <c r="D6" s="11">
+        <v>44.0</v>
+      </c>
+      <c r="E6" s="17">
+        <v>56892.0</v>
+      </c>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14"/>
+      <c r="B7" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="17">
+        <v>3916.0</v>
+      </c>
+      <c r="D7" s="11">
+        <v>17.0</v>
+      </c>
+      <c r="E7" s="17">
+        <v>66572.0</v>
+      </c>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="14"/>
+      <c r="B8" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="19">
+        <v>1103003.0</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14"/>
+      <c r="B11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="17">
+        <v>1153.0</v>
+      </c>
+      <c r="D11" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="E11" s="17">
+        <v>19027.0</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14"/>
+      <c r="B12" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="11">
+        <v>300.0</v>
+      </c>
+      <c r="D12" s="11">
+        <v>44.0</v>
+      </c>
+      <c r="E12" s="17">
+        <v>13200.0</v>
+      </c>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14"/>
+      <c r="B13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="11">
+        <v>500.0</v>
+      </c>
+      <c r="D13" s="11">
+        <v>17.0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>8500.0</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14"/>
+      <c r="B14" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C14" s="11">
+        <v>375.0</v>
+      </c>
+      <c r="D14" s="11">
+        <v>18.4</v>
+      </c>
+      <c r="E14" s="17">
+        <v>6904.0</v>
+      </c>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14"/>
+      <c r="B15" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="19">
+        <v>47631.0</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14"/>
+      <c r="B18" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C18" s="17">
+        <v>46703.0</v>
+      </c>
+      <c r="D18" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="E18" s="17">
+        <v>770603.0</v>
+      </c>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14"/>
+      <c r="B19" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="17">
+        <v>3736.0</v>
+      </c>
+      <c r="D19" s="11">
+        <v>17.0</v>
+      </c>
+      <c r="E19" s="17">
+        <v>63516.0</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14"/>
+      <c r="B20" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C20" s="11">
+        <v>374.0</v>
+      </c>
+      <c r="D20" s="11">
+        <v>44.0</v>
+      </c>
+      <c r="E20" s="17">
+        <v>16440.0</v>
+      </c>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14"/>
+      <c r="B21" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="17">
+        <v>2000.0</v>
+      </c>
+      <c r="D21" s="11">
+        <v>18.4</v>
+      </c>
+      <c r="E21" s="17">
+        <v>36820.0</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="14"/>
+      <c r="B22" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="19">
+        <v>887379.0</v>
+      </c>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="12"/>
-      <c r="B3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C3" s="19">
-        <v>47741.0</v>
-      </c>
-      <c r="D3" s="10">
-        <v>16.5</v>
-      </c>
-      <c r="E3" s="19">
-        <v>787728.0</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="12"/>
-      <c r="B4" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="C4" s="19">
-        <v>4151.0</v>
-      </c>
-      <c r="D4" s="10">
-        <v>38.0</v>
-      </c>
-      <c r="E4" s="19">
-        <v>157753.0</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="12"/>
-      <c r="B5" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="19">
-        <v>1850.0</v>
-      </c>
-      <c r="D5" s="10">
-        <v>18.4</v>
-      </c>
-      <c r="E5" s="19">
-        <v>34059.0</v>
-      </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="12"/>
-      <c r="B6" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C6" s="19">
-        <v>1293.0</v>
-      </c>
-      <c r="D6" s="10">
-        <v>44.0</v>
-      </c>
-      <c r="E6" s="19">
-        <v>56892.0</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="12"/>
-      <c r="B7" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="19">
-        <v>3916.0</v>
-      </c>
-      <c r="D7" s="10">
-        <v>17.0</v>
-      </c>
-      <c r="E7" s="19">
-        <v>66572.0</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12"/>
-      <c r="B8" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="22">
+      <c r="B25" s="24">
+        <v>66.73</v>
+      </c>
+      <c r="C25" s="25">
         <v>1103003.0</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12"/>
-      <c r="B11" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" s="19">
-        <v>1153.0</v>
-      </c>
-      <c r="D11" s="10">
-        <v>16.5</v>
-      </c>
-      <c r="E11" s="19">
-        <v>19027.0</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="12"/>
-      <c r="B12" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="C12" s="10">
-        <v>300.0</v>
-      </c>
-      <c r="D12" s="10">
-        <v>44.0</v>
-      </c>
-      <c r="E12" s="19">
-        <v>13200.0</v>
-      </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="12"/>
-      <c r="B13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="10">
-        <v>500.0</v>
-      </c>
-      <c r="D13" s="10">
-        <v>17.0</v>
-      </c>
-      <c r="E13" s="19">
-        <v>8500.0</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12"/>
-      <c r="B14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="10">
-        <v>375.0</v>
-      </c>
-      <c r="D14" s="10">
-        <v>18.4</v>
-      </c>
-      <c r="E14" s="19">
-        <v>6904.0</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="12"/>
-      <c r="B15" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="22">
+      <c r="D25" s="24">
+        <v>897.8</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="27" t="s">
+        <v>100</v>
+      </c>
+      <c r="H25" s="27" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B26" s="24">
+        <v>402.8</v>
+      </c>
+      <c r="C26" s="25">
         <v>47631.0</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12"/>
-      <c r="B18" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C18" s="19">
-        <v>46703.0</v>
-      </c>
-      <c r="D18" s="10">
-        <v>16.5</v>
-      </c>
-      <c r="E18" s="19">
-        <v>770603.0</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="12"/>
-      <c r="B19" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="C19" s="19">
-        <v>3736.0</v>
-      </c>
-      <c r="D19" s="10">
-        <v>17.0</v>
-      </c>
-      <c r="E19" s="19">
-        <v>63516.0</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12"/>
-      <c r="B20" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C20" s="10">
-        <v>374.0</v>
-      </c>
-      <c r="D20" s="10">
-        <v>44.0</v>
-      </c>
-      <c r="E20" s="19">
-        <v>16440.0</v>
-      </c>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="12"/>
-      <c r="B21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="19">
-        <v>2000.0</v>
-      </c>
-      <c r="D21" s="10">
-        <v>18.4</v>
-      </c>
-      <c r="E21" s="19">
-        <v>36820.0</v>
-      </c>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="12"/>
-      <c r="B22" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="22">
+      <c r="D26" s="24">
+        <v>6.4</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="F26" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="H26" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="24">
+        <v>187.2</v>
+      </c>
+      <c r="C27" s="25">
         <v>887379.0</v>
       </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="12"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="D27" s="24">
+        <v>257.5</v>
+      </c>
+      <c r="E27" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="F27" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G27" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H27" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B25" s="25">
-        <v>66.73</v>
-      </c>
-      <c r="C25" s="26">
-        <v>1103003.0</v>
-      </c>
-      <c r="D25" s="25">
-        <v>897.8</v>
-      </c>
-      <c r="E25" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="F25" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="G25" s="27" t="s">
+    </row>
+    <row r="28">
+      <c r="A28" s="7" t="s">
         <v>108</v>
-      </c>
-      <c r="H25" s="27" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B26" s="25">
-        <v>402.8</v>
-      </c>
-      <c r="C26" s="26">
-        <v>47631.0</v>
-      </c>
-      <c r="D26" s="25">
-        <v>6.4</v>
-      </c>
-      <c r="E26" s="27" t="s">
-        <v>111</v>
-      </c>
-      <c r="F26" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="H26" s="27" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="25">
-        <v>187.2</v>
-      </c>
-      <c r="C27" s="26">
-        <v>887379.0</v>
-      </c>
-      <c r="D27" s="25">
-        <v>257.5</v>
-      </c>
-      <c r="E27" s="27" t="s">
-        <v>105</v>
-      </c>
-      <c r="F27" s="27" t="s">
-        <v>107</v>
-      </c>
-      <c r="G27" s="27" t="s">
-        <v>108</v>
-      </c>
-      <c r="H27" s="27" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="s">
-        <v>114</v>
       </c>
       <c r="B28" s="28">
         <v>656.727</v>
@@ -6319,16 +6319,16 @@
         <v>168.565372</v>
       </c>
       <c r="E28" s="29" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="F28" s="29" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="H28" s="29" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -6347,201 +6347,201 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>9</v>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="8">
+      <c r="A2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="13">
         <v>66.73</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="10">
+      <c r="C2" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="11">
         <v>1.0</v>
       </c>
       <c r="E2" s="9">
         <v>2.0</v>
       </c>
-      <c r="F2" s="8">
+      <c r="F2" s="13">
         <v>2.0</v>
       </c>
-      <c r="G2" s="10" t="s">
-        <v>24</v>
+      <c r="G2" s="11" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="8">
+      <c r="A3" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="13">
         <v>402.8</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="C3" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="11">
         <v>3.0</v>
       </c>
       <c r="E3" s="9">
         <v>5.0</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="13">
         <v>5.0</v>
       </c>
-      <c r="G3" s="10" t="s">
-        <v>32</v>
+      <c r="G3" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>36</v>
+      <c r="C4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="E4" s="9">
         <v>1.0</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4" s="13">
         <v>1.0</v>
       </c>
-      <c r="G4" s="10" t="s">
-        <v>39</v>
+      <c r="G4" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>36</v>
+      <c r="A5" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="E5" s="9">
         <v>1.0</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5" s="13">
         <v>1.0</v>
       </c>
-      <c r="G5" s="10" t="s">
-        <v>39</v>
+      <c r="G5" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>36</v>
+      <c r="A6" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="E6" s="9">
         <v>2.0</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="13">
         <v>2.0</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>39</v>
+      <c r="G6" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>36</v>
+      <c r="A7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>35</v>
       </c>
       <c r="E7" s="9">
         <v>1.0</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7" s="13">
         <v>1.0</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>39</v>
+      <c r="G7" s="11" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B8" s="8">
+      <c r="A8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="13">
         <v>187.2</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="C8" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="11">
         <v>1.0</v>
       </c>
       <c r="E8" s="9">
         <v>2.0</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="13">
         <v>2.0</v>
       </c>
-      <c r="G8" s="10" t="s">
-        <v>32</v>
+      <c r="G8" s="11" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="17">
+      <c r="A9" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="20">
         <v>14.0</v>
       </c>
-      <c r="G9" s="18"/>
+      <c r="G9" s="21"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
